--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Danish service act</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/policy/dk/aggregate-input</t>
+  </si>
+  <si>
+    <t>Aggregated Triage Input</t>
   </si>
   <si>
     <t>http://ehealth.sundhed.dk/policy/ehealth/coherent-submitted-measurement</t>
@@ -503,7 +509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -588,7 +594,7 @@
         <v>50</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -597,10 +603,10 @@
         <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -609,10 +615,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -650,8 +656,20 @@
       <c r="C12" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="D12" t="s" s="2">
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>60</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-provenance-policies.xlsx
+++ b/fhir/CodeSystem-ehealth-provenance-policies.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
